--- a/Test Scenarios.xlsx
+++ b/Test Scenarios.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\Playwright_Framework1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AUTOMATION_PROJECTS\AI BASED\PLAYWRIGHT\PROJECT1_MCP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F39AF95-5374-427E-9AA2-281C6F4970F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20140458-0909-4FD7-B769-826B5AA4E1F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INTRO" sheetId="1" r:id="rId1"/>
@@ -1182,87 +1182,87 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:4" s="13" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="D2" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="13" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:4" s="13" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:4" s="13" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="D5" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="13" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="14" t="s">
         <v>200</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="D6" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="13" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="14" t="s">
         <v>203</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="12" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1749,17 +1749,17 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:4" s="13" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="12" t="s">
         <v>58</v>
       </c>
     </row>
